--- a/data/may/report april.xlsx
+++ b/data/may/report april.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$I$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$I$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="139">
   <si>
     <t>رقم</t>
   </si>
@@ -68,7 +68,13 @@
     <t>أكادميات</t>
   </si>
   <si>
-    <t>غياب يوم 19 التلات ويوم 24 حتىالان</t>
+    <t xml:space="preserve">غياب يوم 19 التلات </t>
+  </si>
+  <si>
+    <t>1 يوم</t>
+  </si>
+  <si>
+    <t>العيد من 25 الى 28</t>
   </si>
   <si>
     <t xml:space="preserve">إبراهيم محمد أحمد  تراوري </t>
@@ -77,13 +83,19 @@
     <t>مدرب جيم</t>
   </si>
   <si>
+    <t>6 ساعات ونص</t>
+  </si>
+  <si>
     <t>إبراهيم مسعد عبداللطيف</t>
   </si>
   <si>
     <t>إسراء اسحق عمر ادم</t>
   </si>
   <si>
-    <t xml:space="preserve">غياب من يوم 16 17 18 19 20 21 23 </t>
+    <t xml:space="preserve">غياب من يوم 16 17 18 19 20 21 23 24 </t>
+  </si>
+  <si>
+    <t>العيد من 25 الى 28 + اجازه سنويه 8 ايام</t>
   </si>
   <si>
     <t>إسلام أحمد إبراهيم</t>
@@ -92,22 +104,40 @@
     <t>مدرب سباحة</t>
   </si>
   <si>
+    <t>3 ساعات</t>
+  </si>
+  <si>
     <t>أمجد إبراهيم عمر كلنتن</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 30 31 </t>
+  </si>
+  <si>
+    <t>2 يوم</t>
+  </si>
+  <si>
     <t>ايمان محمد زوام منصور</t>
   </si>
   <si>
     <t>علاج طبيعي</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 30 </t>
+  </si>
+  <si>
     <t xml:space="preserve">رانية سيد سالم معمر </t>
   </si>
   <si>
     <t>مدربة جمباز</t>
   </si>
   <si>
-    <t xml:space="preserve">غياب يوم 7 و 18 19 20 21 23 </t>
+    <t>غياب يوم 7 و 18 19 20 21 23 24 + تاخير يوم 5 ساعتين ويوم 14 ساعتين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ساعتين </t>
+  </si>
+  <si>
+    <t>العيد من 25 الى 28 + اجازه سنويه 7 ايام</t>
   </si>
   <si>
     <t>رحاب السيد إبراهيم</t>
@@ -116,7 +146,10 @@
     <t>مدربة سباحة</t>
   </si>
   <si>
-    <t>غياب يوم 2 3 4 5 6 7 9 10 11 12 13 14 25 26 27 28</t>
+    <t>غياب يوم 2 3 4 5 6 7 9 10 11 12 13 14 بدون استئذان</t>
+  </si>
+  <si>
+    <t>12 يوم</t>
   </si>
   <si>
     <t xml:space="preserve">ريم خالد محمد ريحان </t>
@@ -128,51 +161,105 @@
     <t>زينب عبدالقادر</t>
   </si>
   <si>
-    <t xml:space="preserve">غياب يوم 9 25 26 27 28 </t>
+    <t xml:space="preserve">غياب يوم 9 </t>
   </si>
   <si>
     <t>شعبان كمال شعبان</t>
   </si>
   <si>
-    <t>غياب يوم 13 14 16 17 18 19 20 21 23 24 25 26 27 28 30 31</t>
+    <t>غياب يوم 13 14 16 17 18 19 20 21 23 24  30 31</t>
   </si>
   <si>
     <t>صفا الرفاعي</t>
   </si>
   <si>
-    <t xml:space="preserve">غياب يوم 3 16 21 23 24 25 26 27 28 </t>
+    <t xml:space="preserve">غياب يوم 3  21 23 24 </t>
+  </si>
+  <si>
+    <t>العيد من 25 الى 28 + اجازه سنويه 2 يوم</t>
   </si>
   <si>
     <t>صفاء بدر حسين نور محمد</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 25 26 27 28 </t>
+  </si>
+  <si>
     <t xml:space="preserve">عبدالعزيز محمد عباس </t>
   </si>
   <si>
+    <t>غياب الشهر كله ما عدا 31</t>
+  </si>
+  <si>
     <t>فردوس عالم عمر</t>
   </si>
   <si>
+    <t>غياب 25 26 27 28 تاخير 2 واستئذان 2</t>
+  </si>
+  <si>
     <t>كامل عمر عثمان</t>
   </si>
   <si>
     <t>مدرب كرة قدم</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 25 26 27 28 + 20 16 12 </t>
+  </si>
+  <si>
+    <t>3 ايام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 ساعه </t>
+  </si>
+  <si>
     <t>محمد اصف محمد صديق</t>
   </si>
   <si>
+    <t>غياب الشهر كله ما عدا 18</t>
+  </si>
+  <si>
     <t>محمد الششتاوي الصياد</t>
   </si>
   <si>
+    <t>غياب من 9 الى اخر الشهر</t>
+  </si>
+  <si>
+    <t>16 يوم</t>
+  </si>
+  <si>
+    <t>1 ساعه</t>
+  </si>
+  <si>
     <t>حسين حسن دبلول</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 11 12 18 19 20 21 23 </t>
+  </si>
+  <si>
+    <t>7 ايام</t>
+  </si>
+  <si>
+    <t>10 ساعات</t>
+  </si>
+  <si>
     <t>محمد حسن داوود</t>
   </si>
   <si>
+    <t>غياب من 17 الى اخر الشهر</t>
+  </si>
+  <si>
+    <t>9 ايام</t>
+  </si>
+  <si>
+    <t>4 ساعات</t>
+  </si>
+  <si>
     <t>محمد حسين عمر محمد</t>
   </si>
   <si>
+    <t>غياب طول الشهر</t>
+  </si>
+  <si>
     <t>محمد نصر محمد موسى</t>
   </si>
   <si>
@@ -188,9 +275,21 @@
     <t>هبة عبدالرحيم حسين محمد</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 9 17 19 21 24 </t>
+  </si>
+  <si>
+    <t>3 ساعاات ونص</t>
+  </si>
+  <si>
+    <t>العيد من 25 الى 28 + اجازه سنويه 4 ايام</t>
+  </si>
+  <si>
     <t>يعقوب عبدالرسول العسلي</t>
   </si>
   <si>
+    <t>غياب يوم 30 وطول الشهر بصم مره واحده ف  اليوم</t>
+  </si>
+  <si>
     <t>علياء الحازمى</t>
   </si>
   <si>
@@ -206,6 +305,9 @@
     <t>customer service</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 5 9 10 11 12 13 14 </t>
+  </si>
+  <si>
     <t>Fahd</t>
   </si>
   <si>
@@ -215,49 +317,97 @@
     <t>مشارى</t>
   </si>
   <si>
+    <t>شيماء</t>
+  </si>
+  <si>
+    <t>العيد من 25 الى 28 + 2 يوم اجازه سنويه</t>
+  </si>
+  <si>
     <t>محمد مبارك</t>
   </si>
   <si>
     <t>عامل</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 1 2 3 4 6 8 9 10 </t>
+  </si>
+  <si>
     <t>سميرة</t>
   </si>
   <si>
+    <t>غياب  10 8 15 22</t>
+  </si>
+  <si>
     <t>توتال</t>
   </si>
   <si>
+    <t>مبصمش طول الشهر</t>
+  </si>
+  <si>
     <t>موكبير</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 1 2 5  9 14 16 23 </t>
+  </si>
+  <si>
     <t>رحيمه</t>
   </si>
   <si>
+    <t>غياب 8 22 24</t>
+  </si>
+  <si>
     <t>اسماعيل</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 1 5 6 8 15 16 17 22 </t>
+  </si>
+  <si>
     <t>رويده</t>
   </si>
   <si>
+    <t>غياب 2 7 8 9 15 16 22 23 24 30</t>
+  </si>
+  <si>
     <t>فايزه</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 24 23 22 16 9 </t>
+  </si>
+  <si>
     <t>سلطان</t>
   </si>
   <si>
+    <t>غياب 1 9 16 21 22 30 31</t>
+  </si>
+  <si>
     <t>اريام</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 31  18 7 2 </t>
+  </si>
+  <si>
     <t>عبودى</t>
   </si>
   <si>
+    <t>غياب 9 15 16 18 21 22 23 24 30</t>
+  </si>
+  <si>
     <t>سهام</t>
   </si>
   <si>
+    <t>غياب 9 16 22 23 24 31</t>
+  </si>
+  <si>
     <t>امينه</t>
   </si>
   <si>
+    <t xml:space="preserve">غياب 12 7 9 18 20 22 </t>
+  </si>
+  <si>
     <t>امير</t>
+  </si>
+  <si>
+    <t>غياب 2 7 9 18 22 24 31</t>
   </si>
   <si>
     <t>انس</t>
@@ -483,7 +633,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,6 +661,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +1088,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -950,16 +1112,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -968,89 +1130,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1087,22 +1249,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1425,7 +1597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6.88888888888889" style="2" customWidth="1"/>
@@ -1435,8 +1607,8 @@
     <col min="5" max="5" width="10.7962962962963" style="2" customWidth="1"/>
     <col min="6" max="6" width="104.842592592593" style="2" customWidth="1"/>
     <col min="7" max="7" width="30.9444444444444" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="43.8333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.8981481481481" style="2" customWidth="1"/>
+    <col min="9" max="9" width="51.4444444444444" style="2" customWidth="1"/>
     <col min="10" max="10" width="31.6944444444444" style="8" customWidth="1"/>
     <col min="11" max="16379" width="9.13888888888889" style="2"/>
     <col min="16380" max="16384" width="9" style="2"/>
@@ -1506,20 +1678,24 @@
       <c r="F3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="16" t="s">
+        <v>13</v>
+      </c>
       <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A4" s="16">
         <v>41</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="16">
         <v>15</v>
@@ -1527,17 +1703,22 @@
       <c r="E4" s="16">
         <v>23</v>
       </c>
+      <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="H4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A5" s="16">
         <v>133</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>11</v>
@@ -1551,15 +1732,17 @@
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
+      <c r="I5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A6" s="16">
         <v>72</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>11</v>
@@ -1571,40 +1754,46 @@
         <v>21</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
+      <c r="I6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A7" s="16">
         <v>73</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="19"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A8" s="16">
         <v>40</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" s="16">
         <v>14</v>
@@ -1612,43 +1801,55 @@
       <c r="E8" s="16">
         <v>22</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="F8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="I8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="23.4" spans="1:11">
-      <c r="A9" s="16">
+      <c r="A9" s="20">
         <v>104</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="16">
+      <c r="B9" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="20">
         <v>10</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="20">
         <v>18</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="16"/>
+      <c r="F9" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A10" s="16">
         <v>109</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D10" s="16">
         <v>17</v>
@@ -1657,22 +1858,26 @@
         <v>21</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
+      <c r="H10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="19"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A11" s="16">
         <v>77</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D11" s="16">
         <v>8</v>
@@ -1681,65 +1886,75 @@
         <v>16</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="16"/>
+        <v>38</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
+      <c r="I11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A12" s="16">
         <v>106</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="19">
+        <v>41</v>
+      </c>
+      <c r="D12" s="23">
         <v>8</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="23">
         <v>16</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
+      <c r="I12" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="19"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A13" s="16">
         <v>39</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="B13" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="20">
         <v>17</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="20">
         <v>21</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="16"/>
+      <c r="F13" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="19"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A14" s="16">
         <v>134</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>11</v>
@@ -1751,19 +1966,23 @@
         <v>21</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="16"/>
+        <v>45</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
+      <c r="I14" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A15" s="16">
         <v>122</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>11</v>
@@ -1775,22 +1994,26 @@
         <v>23</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="16"/>
+        <v>47</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>13</v>
+      </c>
       <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
+      <c r="I15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="19"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="23.4" spans="1:11">
       <c r="A16" s="16">
         <v>128</v>
       </c>
       <c r="B16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>37</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>27</v>
       </c>
       <c r="D16" s="16">
         <v>15</v>
@@ -1798,39 +2021,47 @@
       <c r="E16" s="16">
         <v>23</v>
       </c>
-      <c r="F16" s="16"/>
+      <c r="F16" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
+      <c r="I16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="23.4" spans="1:14">
-      <c r="A17" s="16">
+      <c r="A17" s="24">
         <v>101</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
+      <c r="B17" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A18" s="16">
         <v>98</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18" s="16">
         <v>14</v>
@@ -1838,21 +2069,27 @@
       <c r="E18" s="16">
         <v>22</v>
       </c>
-      <c r="F18" s="16"/>
+      <c r="F18" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
+      <c r="H18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A19" s="16">
         <v>3</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D19" s="16">
         <v>17</v>
@@ -1860,118 +2097,158 @@
       <c r="E19" s="16">
         <v>21</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="F19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="23.4" spans="1:14">
-      <c r="A20" s="20">
+      <c r="A20" s="24">
         <v>86</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="20">
-        <v>14</v>
-      </c>
-      <c r="E20" s="20">
+      <c r="B20" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="24">
+        <v>14</v>
+      </c>
+      <c r="E20" s="24">
         <v>22</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
+      <c r="F20" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" s="3" customFormat="1" ht="23.4" spans="1:14">
-      <c r="A21" s="16">
+      <c r="A21" s="24">
         <v>56</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="N21" s="21"/>
+      <c r="B21" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="N21" s="16"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A22" s="16">
         <v>7</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
+      <c r="F22" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A23" s="16">
         <v>70</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="F23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="23.4" spans="1:14">
-      <c r="A24" s="16">
+      <c r="A24" s="24">
         <v>49</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="24">
         <v>8</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="24">
         <v>12</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
+      <c r="F24" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A25" s="16">
         <v>14</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D25" s="16">
         <v>17</v>
@@ -1979,18 +2256,22 @@
       <c r="E25" s="16">
         <v>21</v>
       </c>
-      <c r="F25" s="16"/>
+      <c r="F25" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
+      <c r="I25" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A26" s="16">
         <v>135</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>11</v>
@@ -2001,21 +2282,25 @@
       <c r="E26" s="16">
         <v>21</v>
       </c>
-      <c r="F26" s="16"/>
+      <c r="F26" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
+      <c r="I26" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A27" s="16">
         <v>82</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D27" s="16">
         <v>12</v>
@@ -2023,40 +2308,46 @@
       <c r="E27" s="16">
         <v>20</v>
       </c>
-      <c r="F27" s="16"/>
+      <c r="F27" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
+      <c r="I27" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="23.4" spans="1:14">
-      <c r="A28" s="16">
+      <c r="A28" s="24">
         <v>127</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="B28" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="24">
         <v>18</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="24">
         <v>22</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="16"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="19"/>
     </row>
     <row r="29" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A29" s="16">
         <v>91</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>11</v>
@@ -2067,39 +2358,53 @@
       <c r="E29" s="16">
         <v>21</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
+      <c r="F29" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="19"/>
     </row>
     <row r="30" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A30" s="16">
         <v>4</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="F30" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>13</v>
+      </c>
       <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
+      <c r="I30" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A31" s="16">
         <v>138</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D31" s="16">
         <v>15</v>
@@ -2110,559 +2415,673 @@
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
+      <c r="I31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="19"/>
     </row>
     <row r="32" s="3" customFormat="1" ht="23.4" spans="1:14">
       <c r="A32" s="16">
         <v>2</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
+        <v>88</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
+      <c r="I32" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" s="5" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A33" s="16">
+      <c r="A33" s="24">
         <v>16</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
+      <c r="B33" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="19"/>
     </row>
     <row r="34" s="5" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A34" s="22">
+      <c r="A34" s="28">
         <v>19</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
+      <c r="B34" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" s="6" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A35" s="23">
+      <c r="A35" s="30">
         <v>21</v>
       </c>
-      <c r="B35" s="23" t="s">
-        <v>60</v>
+      <c r="B35" s="30" t="s">
+        <v>94</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="16"/>
-    </row>
-    <row r="36" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A36" s="24">
+        <v>90</v>
+      </c>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="19"/>
+    </row>
+    <row r="36" s="6" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A36" s="30">
+        <v>37</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" s="19"/>
+    </row>
+    <row r="37" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A37" s="31">
         <v>5</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B37" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="32"/>
+    </row>
+    <row r="38" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A38" s="31">
+        <v>8</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="32"/>
+    </row>
+    <row r="39" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A39" s="31">
+        <v>9</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="32"/>
+    </row>
+    <row r="40" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A40" s="31">
+        <v>13</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="32"/>
+    </row>
+    <row r="41" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A41" s="31">
+        <v>26</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="32"/>
+    </row>
+    <row r="42" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A42" s="31">
+        <v>53</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="32"/>
+    </row>
+    <row r="43" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A43" s="31">
+        <v>55</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="32"/>
+    </row>
+    <row r="44" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A44" s="31">
         <v>61</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="23"/>
-    </row>
-    <row r="37" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A37" s="24">
-        <v>8</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="23"/>
-    </row>
-    <row r="38" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A38" s="24">
-        <v>9</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="23"/>
-    </row>
-    <row r="39" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A39" s="24">
-        <v>13</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="23"/>
-    </row>
-    <row r="40" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A40" s="24">
-        <v>26</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="23"/>
-    </row>
-    <row r="41" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A41" s="24">
-        <v>53</v>
-      </c>
-      <c r="B41" s="24" t="s">
+      <c r="B44" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="32"/>
+    </row>
+    <row r="45" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A45" s="31">
+        <v>90</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="32"/>
+    </row>
+    <row r="46" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A46" s="31">
+        <v>92</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="32"/>
+    </row>
+    <row r="47" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A47" s="31">
+        <v>93</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="32"/>
+    </row>
+    <row r="48" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A48" s="31">
+        <v>105</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="32"/>
+    </row>
+    <row r="49" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A49" s="31">
+        <v>107</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="32"/>
+    </row>
+    <row r="50" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A50" s="31">
+        <v>112</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="32"/>
+    </row>
+    <row r="51" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A51" s="31">
+        <v>118</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="32"/>
+    </row>
+    <row r="52" s="7" customFormat="1" ht="23.4" spans="1:10">
+      <c r="A52" s="33">
+        <v>12</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="34"/>
+    </row>
+    <row r="53" ht="23.4" spans="1:10">
+      <c r="A53" s="33">
         <v>67</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="23"/>
-    </row>
-    <row r="42" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A42" s="24">
-        <v>55</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="23"/>
-    </row>
-    <row r="43" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A43" s="24">
-        <v>61</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="23"/>
-    </row>
-    <row r="44" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A44" s="24">
-        <v>90</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="23"/>
-    </row>
-    <row r="45" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A45" s="24">
-        <v>92</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="23"/>
-    </row>
-    <row r="46" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A46" s="24">
-        <v>93</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="23"/>
-    </row>
-    <row r="47" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A47" s="24">
-        <v>105</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="23"/>
-    </row>
-    <row r="48" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A48" s="24">
-        <v>107</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="23"/>
-    </row>
-    <row r="49" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A49" s="24">
-        <v>112</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="23"/>
-    </row>
-    <row r="50" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A50" s="24">
-        <v>118</v>
-      </c>
-      <c r="B50" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="23"/>
-    </row>
-    <row r="51" s="7" customFormat="1" ht="23.4" spans="1:10">
-      <c r="A51" s="25">
-        <v>12</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="26"/>
-    </row>
-    <row r="52" ht="23.4" spans="1:10">
-      <c r="A52" s="25">
-        <v>67</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="25"/>
-    </row>
-    <row r="53" ht="23.4" spans="1:10">
-      <c r="A53" s="25">
+      <c r="B53" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+    </row>
+    <row r="54" ht="23.4" spans="1:10">
+      <c r="A54" s="33">
         <v>80</v>
       </c>
-      <c r="B53" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="25"/>
-    </row>
-    <row r="54" ht="23.4" spans="1:10">
-      <c r="A54" s="25">
+      <c r="B54" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+    </row>
+    <row r="55" ht="23.4" spans="1:10">
+      <c r="A55" s="33">
         <v>94</v>
       </c>
-      <c r="B54" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-    </row>
-    <row r="55" ht="23.4" spans="1:10">
-      <c r="A55" s="25">
+      <c r="B55" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+    </row>
+    <row r="56" ht="23.4" spans="1:10">
+      <c r="A56" s="33">
         <v>113</v>
       </c>
-      <c r="B55" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-    </row>
-    <row r="56" ht="23.4" spans="1:10">
-      <c r="A56" s="25">
+      <c r="B56" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+    </row>
+    <row r="57" ht="23.4" spans="1:10">
+      <c r="A57" s="33">
         <v>114</v>
       </c>
-      <c r="B56" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-    </row>
-    <row r="57" ht="23.4" spans="1:10">
-      <c r="A57" s="25">
+      <c r="B57" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+    </row>
+    <row r="58" ht="23.4" spans="1:10">
+      <c r="A58" s="33">
         <v>115</v>
       </c>
-      <c r="B57" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-    </row>
-    <row r="58" ht="23.4" spans="1:10">
-      <c r="A58" s="25">
+      <c r="B58" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" s="33"/>
+      <c r="H58" s="33"/>
+      <c r="I58" s="33"/>
+    </row>
+    <row r="59" ht="23.4" spans="1:10">
+      <c r="A59" s="33">
         <v>116</v>
       </c>
-      <c r="B58" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
-      <c r="I58" s="25"/>
-    </row>
-    <row r="59" ht="23.4" spans="1:10">
-      <c r="A59" s="25">
+      <c r="B59" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+    </row>
+    <row r="60" ht="23.4" spans="1:10">
+      <c r="A60" s="33">
         <v>120</v>
       </c>
-      <c r="B59" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="25"/>
-      <c r="I59" s="25"/>
-    </row>
-    <row r="60" ht="23.4" spans="1:10">
-      <c r="A60" s="25">
+      <c r="B60" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+    </row>
+    <row r="61" ht="23.4" spans="1:10">
+      <c r="A61" s="33">
         <v>129</v>
       </c>
-      <c r="B60" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
-    </row>
-    <row r="61" ht="23.4" spans="1:10">
-      <c r="A61" s="25">
+      <c r="B61" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="33"/>
+    </row>
+    <row r="62" ht="23.4" spans="1:10">
+      <c r="A62" s="33">
         <v>131</v>
       </c>
-      <c r="B61" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-    </row>
-    <row r="62" ht="23.4" spans="1:10">
-      <c r="A62" s="25">
+      <c r="B62" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+    </row>
+    <row r="63" ht="23.4" spans="1:10">
+      <c r="A63" s="33">
         <v>132</v>
       </c>
-      <c r="B62" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="25"/>
+      <c r="B63" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I62" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="B1:I62">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:I63" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="B1:I63">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
